--- a/data/trans_orig/IP05A01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP05A01-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55700</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23715</t>
+          <t>23801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43479</t>
+          <t>42707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60602</t>
+          <t>60201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46718</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63209</t>
+          <t>62443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51900</t>
+          <t>50692</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68447</t>
+          <t>67954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103412</t>
+          <t>103111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126322</t>
+          <t>126838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26791</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>43151</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>34644</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66413</t>
+          <t>66596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>87786</t>
+          <t>87930</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,81%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>25597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57387</t>
+          <t>57079</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25118</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38190</t>
+          <t>39086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56020</t>
+          <t>54896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73559</t>
+          <t>73771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,49%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33531</t>
+          <t>33415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27514</t>
+          <t>26728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40356</t>
+          <t>40663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48789</t>
+          <t>48979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69004</t>
+          <t>69317</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31721</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46251</t>
+          <t>45252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30054</t>
+          <t>30410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43305</t>
+          <t>43920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>66149</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86180</t>
+          <t>85696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24517</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25733</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>35611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24957</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53344</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67783</t>
+          <t>67803</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>19210</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31078</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>15169</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>29804</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>35448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52319</t>
+          <t>52455</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>24210</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36331</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24991</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36641</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51993</t>
+          <t>52326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69685</t>
+          <t>69967</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53857</t>
+          <t>53342</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>72343</t>
+          <t>71018</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55265</t>
+          <t>56555</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74711</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114380</t>
+          <t>113992</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>141515</t>
+          <t>141057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>36107</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53764</t>
+          <t>54466</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36913</t>
+          <t>37355</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55238</t>
+          <t>55568</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>78927</t>
+          <t>79130</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>103761</t>
+          <t>103666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27841</t>
+          <t>27718</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31776</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>35234</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>55294</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>90716</t>
+          <t>90400</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>110272</t>
+          <t>109289</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>94877</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>114927</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>192386</t>
+          <t>191840</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>219277</t>
+          <t>218855</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>40817</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>59944</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>40452</t>
+          <t>40944</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>59680</t>
+          <t>60073</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>86749</t>
+          <t>86536</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>113024</t>
+          <t>113444</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>323385</t>
+          <t>323949</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>365850</t>
+          <t>366486</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>342348</t>
+          <t>342035</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>384980</t>
+          <t>384899</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>676747</t>
+          <t>679411</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>738378</t>
+          <t>740120</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>240528</t>
+          <t>240003</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>279749</t>
+          <t>280691</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>263387</t>
+          <t>263559</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>306490</t>
+          <t>305865</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>515998</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>573587</t>
+          <t>572135</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>63446</t>
+          <t>62918</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>89801</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>60893</t>
+          <t>62989</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>86700</t>
+          <t>86810</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>130631</t>
+          <t>132373</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>167863</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>40736</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34772</t>
+          <t>33153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47722</t>
+          <t>47148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67455</t>
+          <t>67469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84712</t>
+          <t>85951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21162</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36626</t>
+          <t>36636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>13651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66954</t>
+          <t>66842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82599</t>
+          <t>82305</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68015</t>
+          <t>67467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83631</t>
+          <t>83325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140813</t>
+          <t>139871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162379</t>
+          <t>161359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,75%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35797</t>
+          <t>36525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>37554</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41895</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54507</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>42339</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55382</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89176</t>
+          <t>88784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106541</t>
+          <t>106068</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25381</t>
+          <t>24549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15036</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47375</t>
+          <t>47846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45551</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59308</t>
+          <t>59077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50892</t>
+          <t>51482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65301</t>
+          <t>65662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>101592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120594</t>
+          <t>120871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,55%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>43128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20347</t>
+          <t>21215</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31628</t>
+          <t>31782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29642</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40035</t>
+          <t>39362</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54181</t>
+          <t>54238</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69151</t>
+          <t>69238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,38%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>37387</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48490</t>
+          <t>48757</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>68135</t>
+          <t>67602</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85631</t>
+          <t>84674</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42503</t>
+          <t>42738</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>446</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84215</t>
+          <t>84323</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>102060</t>
+          <t>102701</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>82596</t>
+          <t>82983</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>101491</t>
+          <t>101590</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>172966</t>
+          <t>172248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>199541</t>
+          <t>199562</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,16%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>29994</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46403</t>
+          <t>47442</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36603</t>
+          <t>36028</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54694</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70694</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95648</t>
+          <t>95563</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>114697</t>
+          <t>115455</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>132888</t>
+          <t>133361</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>126640</t>
+          <t>125518</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>144107</t>
+          <t>143395</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>247976</t>
+          <t>248402</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>272055</t>
+          <t>272007</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>24902</t>
+          <t>24347</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>41215</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>22015</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>49950</t>
+          <t>49300</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>72825</t>
+          <t>72054</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>21116</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>469831</t>
+          <t>469710</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>510101</t>
+          <t>510833</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>510562</t>
+          <t>511230</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>551618</t>
+          <t>551502</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>992589</t>
+          <t>987403</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1051560</t>
+          <t>1050925</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>150928</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>188598</t>
+          <t>188563</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>159966</t>
+          <t>160620</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>199485</t>
+          <t>199076</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>322517</t>
+          <t>323916</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>374905</t>
+          <t>378261</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>62589</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>54484</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>77907</t>
+          <t>76671</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>108353</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>29983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41530</t>
+          <t>41577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46195</t>
+          <t>46377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67124</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>84665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>25495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41680</t>
+          <t>41849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62418</t>
+          <t>61839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78054</t>
+          <t>77233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69321</t>
+          <t>68661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84938</t>
+          <t>84729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135860</t>
+          <t>137135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157911</t>
+          <t>159199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>36121</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>43532</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64103</t>
+          <t>63878</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20655</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50231</t>
+          <t>50242</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60720</t>
+          <t>61005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52856</t>
+          <t>52845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63012</t>
+          <t>63462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107196</t>
+          <t>107008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120567</t>
+          <t>121701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>27258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43568</t>
+          <t>43769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57409</t>
+          <t>57277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>48757</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62617</t>
+          <t>63366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96466</t>
+          <t>96455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116744</t>
+          <t>115818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,78%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39447</t>
+          <t>38919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>27651</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>22317</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33492</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48743</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63836</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>17776</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31326</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49542</t>
+          <t>49083</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47498</t>
+          <t>47362</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55511</t>
+          <t>55504</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>91459</t>
+          <t>90589</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>102935</t>
+          <t>103099</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>783</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>745</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84847</t>
+          <t>83596</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>101602</t>
+          <t>101539</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75712</t>
+          <t>74735</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>94473</t>
+          <t>94369</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>165535</t>
+          <t>165402</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192375</t>
+          <t>190918</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28582</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44623</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41718</t>
+          <t>42118</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60777</t>
+          <t>61456</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>75925</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>100421</t>
+          <t>101825</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22644</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>127506</t>
+          <t>127913</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>143584</t>
+          <t>143619</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>134464</t>
+          <t>134944</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>150470</t>
+          <t>150209</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>269076</t>
+          <t>266127</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>289736</t>
+          <t>288913</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>32396</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>33075</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>39491</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>59873</t>
+          <t>60553</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>498193</t>
+          <t>497520</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>535248</t>
+          <t>534620</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>520398</t>
+          <t>520794</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>561319</t>
+          <t>561133</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1027975</t>
+          <t>1031424</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1087717</t>
+          <t>1086688</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>131182</t>
+          <t>131657</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>167669</t>
+          <t>166608</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>142154</t>
+          <t>141837</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>180062</t>
+          <t>179578</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>285007</t>
+          <t>284855</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>335323</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>49561</t>
+          <t>48538</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>66719</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>95610</t>
+          <t>95949</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67332</t>
+          <t>69095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73284</t>
+          <t>73759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78785</t>
+          <t>78790</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145061</t>
+          <t>144496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151404</t>
+          <t>151387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39256</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103645</t>
+          <t>103616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98253</t>
+          <t>98092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114421</t>
+          <t>114681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117842</t>
+          <t>123713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212447</t>
+          <t>212282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19971</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87022</t>
+          <t>90596</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12496</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37405</t>
+          <t>38049</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133147</t>
+          <t>128718</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53968</t>
+          <t>54221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51288</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61021</t>
+          <t>60990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100277</t>
+          <t>100861</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113365</t>
+          <t>113864</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>45339</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58859</t>
+          <t>58432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50328</t>
+          <t>50502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67809</t>
+          <t>68552</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101497</t>
+          <t>101655</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122885</t>
+          <t>123881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39912</t>
+          <t>40615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>517</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>27431</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32904</t>
+          <t>32840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35541</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40020</t>
+          <t>39959</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65491</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71907</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36371</t>
+          <t>35910</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43182</t>
+          <t>43131</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>41194</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52145</t>
+          <t>51930</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81390</t>
+          <t>81252</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93493</t>
+          <t>93347</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>81696</t>
+          <t>82441</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>98397</t>
+          <t>98696</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>85850</t>
+          <t>85566</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111386</t>
+          <t>111698</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>172975</t>
+          <t>173925</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>204095</t>
+          <t>204138</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44911</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39604</t>
+          <t>39818</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65196</t>
+          <t>64945</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>18633</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34729</t>
+          <t>34316</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,47 +16765,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>37345</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>28051</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>49892</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>10,08%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>37345</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>28234</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>49536</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>85737</t>
+          <t>86564</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>103365</t>
+          <t>104155</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>116499</t>
+          <t>114062</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>133597</t>
+          <t>133766</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>208634</t>
+          <t>207465</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>233225</t>
+          <t>232317</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>41731</t>
+          <t>40847</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>34895</t>
+          <t>36726</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>47855</t>
+          <t>48050</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>71247</t>
+          <t>72232</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>443413</t>
+          <t>443232</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>539362</t>
+          <t>540857</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>591604</t>
+          <t>588423</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>632453</t>
+          <t>633833</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1051606</t>
+          <t>1048628</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1159720</t>
+          <t>1160105</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>96740</t>
+          <t>95807</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>196632</t>
+          <t>199282</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>88434</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>125982</t>
+          <t>128318</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>197853</t>
+          <t>197631</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>310250</t>
+          <t>311434</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>55904</t>
+          <t>56694</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>85523</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
